--- a/Nutzerstudie/Assets/Results/Analysis_Output/Entscheidung/00_Entscheidungsaufgabe_Auswertung.xlsx
+++ b/Nutzerstudie/Assets/Results/Analysis_Output/Entscheidung/00_Entscheidungsaufgabe_Auswertung.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Lesehilfe" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelentscheidungen'!$A$1:$K$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelentscheidungen'!$A$1:$K$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Regionswerte'!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlhäufigkeiten'!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Methodenvergleich'!$A$1:$J$4</definedName>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1413,7 +1413,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9bd7378d-a24e-481b-89d2-562509889c3e</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Geringste Unsicherheit bei der gewünschten, prognostizierten Temperatur.</t>
+          <t>Temperatur ok und niedrige unsicherheit</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>140.709</v>
+        <v>116.534</v>
       </c>
       <c r="G23" t="n">
         <v>-3.604896392</v>
@@ -1456,7 +1456,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9bd7378d-a24e-481b-89d2-562509889c3e</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dort sind die meisten Bereiche mit der gewünschten Temperatur bei relativ geringer Unsicherheit.</t>
+          <t>scheint mir am ausgeglichensten.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>410.116</v>
+        <v>127.857</v>
       </c>
       <c r="G24" t="n">
         <v>-19.99693754</v>
@@ -1499,7 +1499,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9bd7378d-a24e-481b-89d2-562509889c3e</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hohe Farbsättigung, daher geringe Unsicherheit. Die Farbe passt von allen Bereichen am besten zu der entsprechenden Temperatur laut Legende.</t>
+          <t>gute temperatur und niedrige unsicherheit</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>203.124</v>
+        <v>95.107</v>
       </c>
       <c r="G25" t="n">
         <v>2.704020264</v>
@@ -1542,7 +1542,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Temperatur ok und niedrige unsicherheit</t>
+          <t>Mittelwert scheint korrekt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>116.534</v>
+        <v>207.086</v>
       </c>
       <c r="G26" t="n">
         <v>-3.604896392</v>
@@ -1585,7 +1585,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>scheint mir am ausgeglichensten.</t>
+          <t>Wegen der geringen Standardabweichung und wegen der Temperatur</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>127.857</v>
+        <v>407.897</v>
       </c>
       <c r="G27" t="n">
         <v>-19.99693754</v>
@@ -1628,7 +1628,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1637,32 +1637,32 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>gute temperatur und niedrige unsicherheit</t>
+          <t>Wegen passender Temperatur und wenigen Kästchen</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>95.107</v>
+        <v>263.922</v>
       </c>
       <c r="G28" t="n">
-        <v>2.704020264</v>
+        <v>-20.09617172</v>
       </c>
       <c r="H28" t="n">
-        <v>14.704020264</v>
+        <v>8.096171720000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6453833007999999</v>
+        <v>1.429650956</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1680,29 +1680,29 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mittelwert scheint korrekt</t>
+          <t xml:space="preserve">Der Temperaturbereich erscheint am beständigsten </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>207.086</v>
+        <v>71.688</v>
       </c>
       <c r="G29" t="n">
-        <v>-3.604896392</v>
+        <v>-0.94865091016</v>
       </c>
       <c r="H29" t="n">
-        <v>8.395103607999999</v>
+        <v>11.05134908984</v>
       </c>
       <c r="I29" t="n">
-        <v>1.424277884</v>
+        <v>3.129501516</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1723,29 +1723,29 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wegen der geringen Standardabweichung und wegen der Temperatur</t>
+          <t xml:space="preserve">Die Region passt am besten hinsichtlich der geforderten -12°C </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>407.897</v>
+        <v>116.19</v>
       </c>
       <c r="G30" t="n">
-        <v>-19.99693754</v>
+        <v>-0.9009721432</v>
       </c>
       <c r="H30" t="n">
-        <v>7.996937540000001</v>
+        <v>11.0990278568</v>
       </c>
       <c r="I30" t="n">
-        <v>1.455844682</v>
+        <v>3.080212368</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -1757,7 +1757,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wegen passender Temperatur und wenigen Kästchen</t>
+          <t>R4 scheint sehr konstant zu liegen und im -12 Temperaturbereich am nächsten</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>263.922</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>-20.09617172</v>
@@ -1800,7 +1800,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1809,29 +1809,29 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der Temperaturbereich erscheint am beständigsten </t>
+          <t>Kaum Abweichung und richtige Temperatur</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>71.688</v>
+        <v>57.038</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.94865091016</v>
+        <v>-3.604896392</v>
       </c>
       <c r="H32" t="n">
-        <v>11.05134908984</v>
+        <v>8.395103607999999</v>
       </c>
       <c r="I32" t="n">
-        <v>3.129501516</v>
+        <v>1.424277884</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1852,32 +1852,32 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Region passt am besten hinsichtlich der geforderten -12°C </t>
+          <t>Geringe Abweichung und im Süden die richtige Temperatur</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>116.19</v>
+        <v>168.142</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.9009721432</v>
+        <v>2.77247876</v>
       </c>
       <c r="H33" t="n">
-        <v>11.0990278568</v>
+        <v>14.77247876</v>
       </c>
       <c r="I33" t="n">
-        <v>3.080212368</v>
+        <v>0.650520978</v>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1895,32 +1895,32 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R4 scheint sehr konstant zu liegen und im -12 Temperaturbereich am nächsten</t>
+          <t>Relativ gesättigt und richtiger Farbton</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>89.59999999999999</v>
+        <v>47.864</v>
       </c>
       <c r="G34" t="n">
-        <v>-20.09617172</v>
+        <v>2.704020264</v>
       </c>
       <c r="H34" t="n">
-        <v>8.096171720000001</v>
+        <v>14.704020264</v>
       </c>
       <c r="I34" t="n">
-        <v>1.429650956</v>
+        <v>0.6453833007999999</v>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1938,32 +1938,32 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Kaum Abweichung und richtige Temperatur</t>
+          <t>für mich sinnvollster Bereich</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>57.038</v>
+        <v>189.749</v>
       </c>
       <c r="G35" t="n">
-        <v>-3.604896392</v>
+        <v>2.78459602</v>
       </c>
       <c r="H35" t="n">
-        <v>8.395103607999999</v>
+        <v>14.78459602</v>
       </c>
       <c r="I35" t="n">
-        <v>1.424277884</v>
+        <v>0.6421452136</v>
       </c>
       <c r="J35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -1972,7 +1972,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Geringe Abweichung und im Süden die richtige Temperatur</t>
+          <t>für mich sinnvollster Bereich</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>168.142</v>
+        <v>22.845</v>
       </c>
       <c r="G36" t="n">
         <v>2.77247876</v>
@@ -2015,7 +2015,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Relativ gesättigt und richtiger Farbton</t>
+          <t>für mich sinnvollster Bereich</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>47.864</v>
+        <v>70.777</v>
       </c>
       <c r="G37" t="n">
         <v>2.704020264</v>
@@ -2058,7 +2058,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Temperatur liegt ungefähr bei 12 °C </t>
+          <t>Region hat gebiete mit ca -12 Grad undgeringer unsicherheit, ansder regionen haben ywar teilweise weniger unsicherheit, aber dann passt di tempaeratur nicht</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>264.661</v>
+        <v>270.875</v>
       </c>
       <c r="G38" t="n">
         <v>-3.604896392</v>
@@ -2101,7 +2101,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2110,41 +2110,41 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>die Temperatur dort  ist ungefäghr −12 °C und die Vorhersage  ist relativ sicher</t>
+          <t>Kombination unsicherheit und gewünschte temperatur erscheint mir dort am passensten, bei gereingere unsicherheit andere regionen passt die temperatur nicht mehr</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>111.417</v>
+        <v>119.011</v>
       </c>
       <c r="G39" t="n">
-        <v>-13.324312746</v>
+        <v>-19.99693754</v>
       </c>
       <c r="H39" t="n">
-        <v>1.324312746</v>
+        <v>7.996937540000001</v>
       </c>
       <c r="I39" t="n">
-        <v>5.06290306</v>
+        <v>1.455844682</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2157,35 +2157,164 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Die anderen regionen haben keine -12 grad oder sind sehr unsicher</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>99.048</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-20.09617172</v>
+      </c>
+      <c r="H40" t="n">
+        <v>8.096171720000001</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Temperatur liegt ungefähr bei 12 °C </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>264.661</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-3.604896392</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8.395103607999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>die Temperatur dort  ist ungefäghr −12 °C und die Vorhersage  ist relativ sicher</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>111.417</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-13.324312746</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.324312746</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.06290306</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Ich wähle R1, weil die Temperatur dort ungefähr −12 °C ist und die Vorhersage ziemlich sicher ist und die Unsicherheit gering ist.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F43" t="n">
         <v>73.56699999999999</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G43" t="n">
         <v>-13.1901063</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H43" t="n">
         <v>1.1901063</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I43" t="n">
         <v>5.4355829</v>
       </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="b">
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K40"/>
+  <autoFilter ref="A1:K43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2612,10 +2741,10 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>15.38461538461539</v>
+        <v>14.28571428571429</v>
       </c>
     </row>
     <row r="3">
@@ -2633,10 +2762,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>7.692307692307693</v>
+        <v>7.142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -2654,10 +2783,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>15.38461538461539</v>
+        <v>14.28571428571429</v>
       </c>
     </row>
     <row r="5">
@@ -2672,13 +2801,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>38.46153846153846</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="6">
@@ -2696,10 +2825,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>23.07692307692308</v>
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -2717,10 +2846,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>15.38461538461539</v>
+        <v>14.28571428571429</v>
       </c>
     </row>
     <row r="8">
@@ -2738,10 +2867,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>7.692307692307693</v>
+        <v>7.142857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -2759,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2780,10 +2909,10 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>53.84615384615385</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -2798,13 +2927,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>23.07692307692308</v>
+        <v>28.57142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -2822,10 +2951,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>7.692307692307693</v>
+        <v>7.142857142857143</v>
       </c>
     </row>
     <row r="13">
@@ -2843,10 +2972,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>23.07692307692308</v>
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -2864,10 +2993,10 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>15.38461538461539</v>
+        <v>14.28571428571429</v>
       </c>
     </row>
     <row r="15">
@@ -2885,10 +3014,10 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>46.15384615384615</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="16">
@@ -2903,13 +3032,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>7.692307692307693</v>
+        <v>14.28571428571429</v>
       </c>
     </row>
   </sheetData>
@@ -2998,16 +3127,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>2.006841486707692</v>
+        <v>1.965613591657142</v>
       </c>
       <c r="D2" t="n">
         <v>1.429650956</v>
       </c>
       <c r="E2" t="n">
-        <v>9.435027689316923</v>
+        <v>9.339395120080001</v>
       </c>
       <c r="F2" t="n">
         <v>8.096171720000001</v>
@@ -3016,13 +3145,13 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>23.07692307692308</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>15.38461538461539</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="3">
@@ -3032,31 +3161,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>1.949884168923077</v>
+        <v>1.857072512428571</v>
       </c>
       <c r="D3" t="n">
         <v>1.455844682</v>
       </c>
       <c r="E3" t="n">
-        <v>8.772588646830771</v>
+        <v>9.201152226342858</v>
       </c>
       <c r="F3" t="n">
         <v>7.996937540000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>23.07692307692308</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>15.38461538461539</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="4">
@@ -3066,31 +3195,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>2.081850854338461</v>
+        <v>1.979014737142857</v>
       </c>
       <c r="D4" t="n">
         <v>1.424277884</v>
       </c>
       <c r="E4" t="n">
-        <v>9.589795130270769</v>
+        <v>9.96085233668</v>
       </c>
       <c r="F4" t="n">
-        <v>8.395103607999999</v>
+        <v>9.723226348920001</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7.692307692307693</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>7.692307692307693</v>
+        <v>7.142857142857142</v>
       </c>
     </row>
   </sheetData>
@@ -3161,16 +3290,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>4.846153846153846</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.068188017638113</v>
+        <v>0.8254203058555569</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -3186,19 +3315,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>4.769230769230769</v>
+        <v>4.785714285714286</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.300887271175982</v>
+        <v>1.251372872462107</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -3211,16 +3340,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>4.769230769230769</v>
+        <v>4.785714285714286</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.480644350378474</v>
+        <v>1.42389343964797</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -3315,7 +3444,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3341,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3393,7 +3522,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3471,7 +3600,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3518,7 +3647,7 @@
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -3585,16 +3714,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>1.450980392156874</v>
+        <v>1.127272727272731</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4840872131311698</v>
+        <v>0.5691357119955995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05580693815987977</v>
+        <v>0.0402597402597404</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -3620,16 +3749,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>1.686274509803928</v>
+        <v>3.309090909090909</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4303582597802257</v>
+        <v>0.1911789354746916</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0648567119155357</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -3655,16 +3784,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05405405405406635</v>
+        <v>0.166666666666673</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9733349348192467</v>
+        <v>0.9200444146293204</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002079002079002552</v>
+        <v>0.005952380952381178</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -3690,16 +3819,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1.714285714285694</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3678794411714424</v>
+        <v>0.4243728456769543</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.06122448979591764</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">

--- a/Nutzerstudie/Assets/Results/Analysis_Output/Entscheidung/00_Entscheidungsaufgabe_Auswertung.xlsx
+++ b/Nutzerstudie/Assets/Results/Analysis_Output/Entscheidung/00_Entscheidungsaufgabe_Auswertung.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Lesehilfe" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelentscheidungen'!$A$1:$K$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelentscheidungen'!$A$1:$K$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Regionswerte'!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlhäufigkeiten'!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Methodenvergleich'!$A$1:$J$4</definedName>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1154,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1163,41 +1163,41 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R5 zu warm, R1 und R2 zu unsicher. Am ausgewogensten wirkt R4 passend</t>
+          <t>R1 scheint am Temperaturstabilsten.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>179.878</v>
+        <v>86.187</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.604896392</v>
+        <v>-13.1901063</v>
       </c>
       <c r="H17" t="n">
-        <v>8.395103607999999</v>
+        <v>1.1901063</v>
       </c>
       <c r="I17" t="n">
-        <v>1.424277884</v>
+        <v>5.4355829</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1206,193 +1206,193 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Entspricht recht gut dem Mittelwert und zeigt eine geringe Abweichung als R1. R3 und R5 sind schon zu warm, R4 scheint mir zu kalt</t>
+          <t>Die anderen Regionen sind zum Teil zu kalt oder zu warm. R1 ist die einzige, die Temperaturstabil scheint.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>217.232</v>
+        <v>134.639</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.99693754</v>
+        <v>-13.324312746</v>
       </c>
       <c r="H18" t="n">
-        <v>7.996937540000001</v>
+        <v>1.324312746</v>
       </c>
       <c r="I18" t="n">
-        <v>1.455844682</v>
+        <v>5.06290306</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Die anderen Regionen sind kälter als -12 Grad.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>98.726</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-20.09617172</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.096171720000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>R5 zu warm, R1 und R2 zu unsicher. Am ausgewogensten wirkt R4 passend</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>179.878</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.604896392</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.395103607999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Entspricht recht gut dem Mittelwert und zeigt eine geringe Abweichung als R1. R3 und R5 sind schon zu warm, R4 scheint mir zu kalt</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>217.232</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-19.99693754</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.996937540000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.455844682</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>VSUP</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">R5 zu warm, R2 zu stark im Grauton, R1 zu viel grau/weiss, R4 scheint mir schon zu kalt
 </t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F22" t="n">
         <v>149.203</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.4606507216</v>
-      </c>
-      <c r="H19" t="n">
-        <v>12.4606507216</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.4988802804</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>verlässliche Temperaturprognose</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>157.969</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.94865091016</v>
-      </c>
-      <c r="H20" t="n">
-        <v>11.05134908984</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.129501516</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>keine zu stark erwartenden Temperaturschwankungen</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>125.227</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-13.324312746</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.324312746</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.06290306</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>überwiegende Temperaturprognose für gewünschte Temperatur</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>150.653</v>
       </c>
       <c r="G22" t="n">
         <v>0.4606507216</v>
@@ -1413,7 +1413,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1422,29 +1422,29 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Temperatur ok und niedrige unsicherheit</t>
+          <t>verlässliche Temperaturprognose</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>116.534</v>
+        <v>157.969</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.604896392</v>
+        <v>-0.94865091016</v>
       </c>
       <c r="H23" t="n">
-        <v>8.395103607999999</v>
+        <v>11.05134908984</v>
       </c>
       <c r="I23" t="n">
-        <v>1.424277884</v>
+        <v>3.129501516</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -1456,7 +1456,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1465,41 +1465,41 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>scheint mir am ausgeglichensten.</t>
+          <t>keine zu stark erwartenden Temperaturschwankungen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>127.857</v>
+        <v>125.227</v>
       </c>
       <c r="G24" t="n">
-        <v>-19.99693754</v>
+        <v>-13.324312746</v>
       </c>
       <c r="H24" t="n">
-        <v>7.996937540000001</v>
+        <v>1.324312746</v>
       </c>
       <c r="I24" t="n">
-        <v>1.455844682</v>
+        <v>5.06290306</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1508,32 +1508,32 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>gute temperatur und niedrige unsicherheit</t>
+          <t>überwiegende Temperaturprognose für gewünschte Temperatur</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>95.107</v>
+        <v>150.653</v>
       </c>
       <c r="G25" t="n">
-        <v>2.704020264</v>
+        <v>0.4606507216</v>
       </c>
       <c r="H25" t="n">
-        <v>14.704020264</v>
+        <v>12.4606507216</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6453833007999999</v>
+        <v>1.4988802804</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -1542,7 +1542,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mittelwert scheint korrekt</t>
+          <t>Temperatur ok und niedrige unsicherheit</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>207.086</v>
+        <v>116.534</v>
       </c>
       <c r="G26" t="n">
         <v>-3.604896392</v>
@@ -1585,7 +1585,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wegen der geringen Standardabweichung und wegen der Temperatur</t>
+          <t>scheint mir am ausgeglichensten.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>407.897</v>
+        <v>127.857</v>
       </c>
       <c r="G27" t="n">
         <v>-19.99693754</v>
@@ -1628,7 +1628,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1637,32 +1637,32 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wegen passender Temperatur und wenigen Kästchen</t>
+          <t>gute temperatur und niedrige unsicherheit</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>263.922</v>
+        <v>95.107</v>
       </c>
       <c r="G28" t="n">
-        <v>-20.09617172</v>
+        <v>2.704020264</v>
       </c>
       <c r="H28" t="n">
-        <v>8.096171720000001</v>
+        <v>14.704020264</v>
       </c>
       <c r="I28" t="n">
-        <v>1.429650956</v>
+        <v>0.6453833007999999</v>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1680,29 +1680,29 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der Temperaturbereich erscheint am beständigsten </t>
+          <t>Mittelwert scheint korrekt</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>71.688</v>
+        <v>207.086</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.94865091016</v>
+        <v>-3.604896392</v>
       </c>
       <c r="H29" t="n">
-        <v>11.05134908984</v>
+        <v>8.395103607999999</v>
       </c>
       <c r="I29" t="n">
-        <v>3.129501516</v>
+        <v>1.424277884</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1723,29 +1723,29 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Die Region passt am besten hinsichtlich der geforderten -12°C </t>
+          <t>Wegen der geringen Standardabweichung und wegen der Temperatur</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>116.19</v>
+        <v>407.897</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9009721432</v>
+        <v>-19.99693754</v>
       </c>
       <c r="H30" t="n">
-        <v>11.0990278568</v>
+        <v>7.996937540000001</v>
       </c>
       <c r="I30" t="n">
-        <v>3.080212368</v>
+        <v>1.455844682</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -1757,7 +1757,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R4 scheint sehr konstant zu liegen und im -12 Temperaturbereich am nächsten</t>
+          <t>Wegen passender Temperatur und wenigen Kästchen</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>89.59999999999999</v>
+        <v>263.922</v>
       </c>
       <c r="G31" t="n">
         <v>-20.09617172</v>
@@ -1800,7 +1800,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1809,29 +1809,29 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kaum Abweichung und richtige Temperatur</t>
+          <t xml:space="preserve">Der Temperaturbereich erscheint am beständigsten </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>57.038</v>
+        <v>71.688</v>
       </c>
       <c r="G32" t="n">
-        <v>-3.604896392</v>
+        <v>-0.94865091016</v>
       </c>
       <c r="H32" t="n">
-        <v>8.395103607999999</v>
+        <v>11.05134908984</v>
       </c>
       <c r="I32" t="n">
-        <v>1.424277884</v>
+        <v>3.129501516</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1852,32 +1852,32 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Geringe Abweichung und im Süden die richtige Temperatur</t>
+          <t xml:space="preserve">Die Region passt am besten hinsichtlich der geforderten -12°C </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>168.142</v>
+        <v>116.19</v>
       </c>
       <c r="G33" t="n">
-        <v>2.77247876</v>
+        <v>-0.9009721432</v>
       </c>
       <c r="H33" t="n">
-        <v>14.77247876</v>
+        <v>11.0990278568</v>
       </c>
       <c r="I33" t="n">
-        <v>0.650520978</v>
+        <v>3.080212368</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1895,32 +1895,32 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Relativ gesättigt und richtiger Farbton</t>
+          <t>R4 scheint sehr konstant zu liegen und im -12 Temperaturbereich am nächsten</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>47.864</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>2.704020264</v>
+        <v>-20.09617172</v>
       </c>
       <c r="H34" t="n">
-        <v>14.704020264</v>
+        <v>8.096171720000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6453833007999999</v>
+        <v>1.429650956</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1938,32 +1938,32 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>für mich sinnvollster Bereich</t>
+          <t>Kaum Abweichung und richtige Temperatur</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>189.749</v>
+        <v>57.038</v>
       </c>
       <c r="G35" t="n">
-        <v>2.78459602</v>
+        <v>-3.604896392</v>
       </c>
       <c r="H35" t="n">
-        <v>14.78459602</v>
+        <v>8.395103607999999</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6421452136</v>
+        <v>1.424277884</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -1972,7 +1972,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>für mich sinnvollster Bereich</t>
+          <t>Geringe Abweichung und im Süden die richtige Temperatur</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>22.845</v>
+        <v>168.142</v>
       </c>
       <c r="G36" t="n">
         <v>2.77247876</v>
@@ -2015,7 +2015,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>für mich sinnvollster Bereich</t>
+          <t>Relativ gesättigt und richtiger Farbton</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>70.777</v>
+        <v>47.864</v>
       </c>
       <c r="G37" t="n">
         <v>2.704020264</v>
@@ -2058,7 +2058,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2067,32 +2067,32 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Region hat gebiete mit ca -12 Grad undgeringer unsicherheit, ansder regionen haben ywar teilweise weniger unsicherheit, aber dann passt di tempaeratur nicht</t>
+          <t>für mich sinnvollster Bereich</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>270.875</v>
+        <v>189.749</v>
       </c>
       <c r="G38" t="n">
-        <v>-3.604896392</v>
+        <v>2.78459602</v>
       </c>
       <c r="H38" t="n">
-        <v>8.395103607999999</v>
+        <v>14.78459602</v>
       </c>
       <c r="I38" t="n">
-        <v>1.424277884</v>
+        <v>0.6421452136</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2101,7 +2101,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2114,28 +2114,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kombination unsicherheit und gewünschte temperatur erscheint mir dort am passensten, bei gereingere unsicherheit andere regionen passt die temperatur nicht mehr</t>
+          <t>für mich sinnvollster Bereich</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>119.011</v>
+        <v>22.845</v>
       </c>
       <c r="G39" t="n">
-        <v>-19.99693754</v>
+        <v>2.77247876</v>
       </c>
       <c r="H39" t="n">
-        <v>7.996937540000001</v>
+        <v>14.77247876</v>
       </c>
       <c r="I39" t="n">
-        <v>1.455844682</v>
+        <v>0.650520978</v>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -2144,7 +2144,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2157,28 +2157,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Die anderen regionen haben keine -12 grad oder sind sehr unsicher</t>
+          <t>für mich sinnvollster Bereich</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>99.048</v>
+        <v>70.777</v>
       </c>
       <c r="G40" t="n">
-        <v>-20.09617172</v>
+        <v>2.704020264</v>
       </c>
       <c r="H40" t="n">
-        <v>8.096171720000001</v>
+        <v>14.704020264</v>
       </c>
       <c r="I40" t="n">
-        <v>1.429650956</v>
+        <v>0.6453833007999999</v>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -2187,7 +2187,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">die Temperatur liegt ungefähr bei 12 °C </t>
+          <t>Region hat gebiete mit ca -12 Grad undgeringer unsicherheit, ansder regionen haben ywar teilweise weniger unsicherheit, aber dann passt di tempaeratur nicht</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>264.661</v>
+        <v>270.875</v>
       </c>
       <c r="G41" t="n">
         <v>-3.604896392</v>
@@ -2230,7 +2230,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2239,41 +2239,41 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>die Temperatur dort  ist ungefäghr −12 °C und die Vorhersage  ist relativ sicher</t>
+          <t>Kombination unsicherheit und gewünschte temperatur erscheint mir dort am passensten, bei gereingere unsicherheit andere regionen passt die temperatur nicht mehr</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>111.417</v>
+        <v>119.011</v>
       </c>
       <c r="G42" t="n">
-        <v>-13.324312746</v>
+        <v>-19.99693754</v>
       </c>
       <c r="H42" t="n">
-        <v>1.324312746</v>
+        <v>7.996937540000001</v>
       </c>
       <c r="I42" t="n">
-        <v>5.06290306</v>
+        <v>1.455844682</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2286,35 +2286,164 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Die anderen regionen haben keine -12 grad oder sind sehr unsicher</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>99.048</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-20.09617172</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8.096171720000001</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Temperatur liegt ungefähr bei 12 °C </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>264.661</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-3.604896392</v>
+      </c>
+      <c r="H44" t="n">
+        <v>8.395103607999999</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>die Temperatur dort  ist ungefäghr −12 °C und die Vorhersage  ist relativ sicher</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>111.417</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-13.324312746</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.324312746</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.06290306</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Ich wähle R1, weil die Temperatur dort ungefähr −12 °C ist und die Vorhersage ziemlich sicher ist und die Unsicherheit gering ist.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F46" t="n">
         <v>73.56699999999999</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G46" t="n">
         <v>-13.1901063</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H46" t="n">
         <v>1.1901063</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I46" t="n">
         <v>5.4355829</v>
       </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="b">
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K43"/>
+  <autoFilter ref="A1:K46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2741,10 +2870,10 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>14.28571428571429</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -2762,10 +2891,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>7.142857142857143</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -2783,10 +2912,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>14.28571428571429</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -2801,13 +2930,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>42.85714285714285</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -2825,10 +2954,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>21.42857142857143</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -2843,13 +2972,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>14.28571428571429</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -2867,10 +2996,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>7.142857142857143</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -2888,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2909,10 +3038,10 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -2930,10 +3059,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>28.57142857142857</v>
+        <v>26.66666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -2948,13 +3077,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>7.142857142857143</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -2972,10 +3101,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>21.42857142857143</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -2993,10 +3122,10 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>14.28571428571429</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3014,10 +3143,10 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3164,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>14.28571428571429</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3127,16 +3256,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>1.965613591657142</v>
+        <v>1.92988274928</v>
       </c>
       <c r="D2" t="n">
         <v>1.429650956</v>
       </c>
       <c r="E2" t="n">
-        <v>9.339395120080001</v>
+        <v>9.256513560074668</v>
       </c>
       <c r="F2" t="n">
         <v>8.096171720000001</v>
@@ -3145,13 +3274,13 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>21.42857142857143</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>14.28571428571428</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3161,16 +3290,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>1.857072512428571</v>
+        <v>2.070794548933333</v>
       </c>
       <c r="D3" t="n">
         <v>1.455844682</v>
       </c>
       <c r="E3" t="n">
-        <v>9.201152226342858</v>
+        <v>8.676029594320001</v>
       </c>
       <c r="F3" t="n">
         <v>7.996937540000001</v>
@@ -3179,13 +3308,13 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>28.57142857142857</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>14.28571428571428</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -3195,31 +3324,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>1.979014737142857</v>
+        <v>2.209452614666666</v>
       </c>
       <c r="D4" t="n">
         <v>1.424277884</v>
       </c>
       <c r="E4" t="n">
-        <v>9.96085233668</v>
+        <v>9.376135934234666</v>
       </c>
       <c r="F4" t="n">
-        <v>9.723226348920001</v>
+        <v>8.395103607999999</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14.28571428571428</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>7.142857142857142</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3290,16 +3419,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>4.714285714285714</v>
+        <v>4.733333333333333</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8254203058555569</v>
+        <v>0.7988086367179803</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -3315,22 +3444,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>4.785714285714286</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.251372872462107</v>
+        <v>1.334523278535216</v>
       </c>
       <c r="F3" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
@@ -3340,16 +3469,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>4.785714285714286</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.42389343964797</v>
+        <v>1.486446705914413</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -3444,7 +3573,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3548,7 +3677,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -3626,7 +3755,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3647,7 +3776,7 @@
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -3714,16 +3843,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>1.127272727272731</v>
+        <v>1.457627118644072</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5691357119955995</v>
+        <v>0.4824810858308426</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0402597402597404</v>
+        <v>0.04858757062146905</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -3749,16 +3878,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>3.309090909090909</v>
+        <v>2.135593220338977</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1911789354746916</v>
+        <v>0.3437651321502594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.07118644067796591</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -3784,16 +3913,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.166666666666673</v>
+        <v>0.6153846153846241</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9200444146293204</v>
+        <v>0.7351414805916813</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005952380952381178</v>
+        <v>0.0205128205128208</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -3819,16 +3948,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1.714285714285694</v>
+        <v>1.73333333333332</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4243728456769543</v>
+        <v>0.4203503845086847</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06122448979591764</v>
+        <v>0.05777777777777734</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
